--- a/stage2/output/enriched_Runs Export Feb 27 2026.xlsx
+++ b/stage2/output/enriched_Runs Export Feb 27 2026.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>recycling and waste management services</t>
+          <t>regional recycling and waste management</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>road freight and contract logistics</t>
+          <t>road haulage and contract logistics</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>managed IT, cyber security and communications services</t>
+          <t>managed IT and cyber security services</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Whiteley</t>
+          <t>Fareham</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>private hospital EHR and patient administration</t>
+          <t>private hospital information systems</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -768,7 +768,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TDS</t>
+          <t>Tyldesley Distribution Services</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>road haulage and pallet distribution</t>
+          <t>palletised distribution and warehousing</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -837,7 +837,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAB Coventry</t>
+          <t>PAB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sheet metal prototyping and production</t>
+          <t>precision sheet metal fabrication and prototyping</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>contract logistics and road haulage</t>
+          <t>road haulage and contract logistics</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1074,7 +1074,11 @@
           <t>Management NOT Founder/Shareholder</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>50-60</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>darren.scott-healey@tmtech.co.uk</t>
@@ -1085,7 +1089,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAB Coventry</t>
+          <t>PAB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1118,7 +1122,11 @@
           <t>Management NOT Founder/Shareholder</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>50-60</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>markb@pabcoventry.co.uk</t>
